--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.11080856456615</v>
+        <v>5.380506391741999</v>
       </c>
       <c r="D2" t="n">
-        <v>33.5643127499667</v>
+        <v>5.454200821869589</v>
       </c>
       <c r="E2" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F2" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.98534711676675</v>
+        <v>3.735118906474597</v>
       </c>
       <c r="D3" t="n">
-        <v>23.40144983026836</v>
+        <v>3.802735597418609</v>
       </c>
       <c r="E3" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F3" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.99613103351123</v>
+        <v>5.524371292945575</v>
       </c>
       <c r="D4" t="n">
-        <v>34.67408598403396</v>
+        <v>5.634538972405519</v>
       </c>
       <c r="E4" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F4" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.92150713589023</v>
+        <v>5.187244909582162</v>
       </c>
       <c r="D5" t="n">
-        <v>32.87756917849207</v>
+        <v>5.342604991504961</v>
       </c>
       <c r="E5" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F5" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.14659077174633</v>
+        <v>5.873821000408779</v>
       </c>
       <c r="D6" t="n">
-        <v>36.33567637211954</v>
+        <v>5.904547410469426</v>
       </c>
       <c r="E6" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F6" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.72396048232418</v>
+        <v>5.64264357837768</v>
       </c>
       <c r="D7" t="n">
-        <v>34.57340851706716</v>
+        <v>5.618178884023415</v>
       </c>
       <c r="E7" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F7" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.35224823850567</v>
+        <v>5.744740338757171</v>
       </c>
       <c r="D8" t="n">
-        <v>35.59917033413129</v>
+        <v>5.784865179296336</v>
       </c>
       <c r="E8" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F8" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.64557002256156</v>
+        <v>3.679905128666254</v>
       </c>
       <c r="D9" t="n">
-        <v>22.85423867334002</v>
+        <v>3.713813784417753</v>
       </c>
       <c r="E9" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F9" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.27484044890066</v>
+        <v>5.732161572946358</v>
       </c>
       <c r="D10" t="n">
-        <v>35.35272355028923</v>
+        <v>5.744817576921999</v>
       </c>
       <c r="E10" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F10" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.68817570027856</v>
+        <v>5.474328551295267</v>
       </c>
       <c r="D11" t="n">
-        <v>33.9533348959495</v>
+        <v>5.517416920591793</v>
       </c>
       <c r="E11" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F11" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.60131209949946</v>
+        <v>5.785213216168662</v>
       </c>
       <c r="D12" t="n">
-        <v>35.81580245555858</v>
+        <v>5.820067899028269</v>
       </c>
       <c r="E12" t="n">
-        <v>4.625126895926734</v>
+        <v>0.7515831205880942</v>
       </c>
       <c r="F12" t="n">
-        <v>4.587357333431447</v>
+        <v>0.7454455666826101</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
